--- a/output/pdf_financials_xlsx/RESO.xlsx
+++ b/output/pdf_financials_xlsx/RESO.xlsx
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.930828</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.93819</v>
       </c>
     </row>
     <row r="18">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.965414</v>
+        <v>-0.965414</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.479095</v>
+        <v>-0.479095</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.965414</v>
+        <v>-0.965414</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.479095</v>
+        <v>-0.479095</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>19.30828</v>
+        <v>-19.30828</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4.356396824186715</v>
+        <v>204.3563968241867</v>
       </c>
     </row>
     <row r="32">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.080067</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.418506</v>
       </c>
     </row>
     <row r="93">
@@ -2518,7 +2518,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.080067</v>
       </c>
@@ -3348,10 +3352,10 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.965414</v>
+        <v>-0.965414</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.479095</v>
+        <v>-0.479095</v>
       </c>
     </row>
     <row r="43">
